--- a/commission/megan/2026-07.xlsx
+++ b/commission/megan/2026-07.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="52">
   <si>
     <t>Equine Performance Labs, LLC</t>
   </si>
@@ -35,6 +35,12 @@
   </si>
   <si>
     <t>Q3 Route C Accelerator — tiered on invoiced revenue when $30K gate met (else standard waterfall)</t>
+  </si>
+  <si>
+    <t>Basis</t>
+  </si>
+  <si>
+    <t>✅ CRM + QuickBooks reconciled (paid on cleared)</t>
   </si>
   <si>
     <t>Route C — Q3 Accelerator</t>
@@ -204,6 +210,11 @@
     <font>
       <b/>
       <color rgb="0F5E4F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="0F5E4F"/>
       <sz val="12"/>
     </font>
     <font>
@@ -227,11 +238,6 @@
     <font>
       <b/>
       <color rgb="FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="0F5E4F"/>
       <sz val="10"/>
     </font>
     <font>
@@ -272,7 +278,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -280,21 +286,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -696,514 +703,522 @@
         <v>7</v>
       </c>
     </row>
+    <row r="4" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>8</v>
+      <c r="A5" s="7" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="7">
+        <v>11</v>
+      </c>
+      <c r="B6" s="8">
         <v>20400</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>10</v>
+      <c r="C6" s="9" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="10">
+      <c r="A7" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="11">
         <v>1020</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="11" t="s">
+      <c r="A9" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="B9" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="C9" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="D9" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="E9" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="F9" s="13" t="s">
         <v>19</v>
       </c>
+      <c r="G9" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="14">
+      <c r="A10" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="15">
         <v>5400</v>
       </c>
-      <c r="H10" s="15">
+      <c r="H10" s="16">
         <v>671.25</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="16">
+      <c r="B11" s="17">
         <v>46217.5</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" s="17">
-        <v>0</v>
-      </c>
-      <c r="G11" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11" s="18" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="F11" s="18">
+        <v>0</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B12" s="16">
+      <c r="B12" s="17">
         <v>46217.5</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" s="17">
+        <v>26</v>
+      </c>
+      <c r="F12" s="18">
         <v>4800</v>
       </c>
-      <c r="G12" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H12" s="18" t="s">
-        <v>23</v>
+      <c r="G12" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="16">
+      <c r="B13" s="17">
         <v>46206.5</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="17">
-        <v>0</v>
-      </c>
-      <c r="G13" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H13" s="18" t="s">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="F13" s="18">
+        <v>0</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" s="19" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B14" s="16">
+      <c r="B14" s="17">
         <v>46206.5</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F14" s="17">
+        <v>28</v>
+      </c>
+      <c r="F14" s="18">
         <v>600</v>
       </c>
-      <c r="G14" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H14" s="18" t="s">
-        <v>23</v>
+      <c r="G14" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14" s="19" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="F16" s="14">
+      <c r="A16" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="15">
         <v>4800</v>
       </c>
-      <c r="H16" s="15">
+      <c r="H16" s="16">
         <v>720</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="16">
+      <c r="B17" s="17">
         <v>46218.5</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F17" s="17">
-        <v>0</v>
-      </c>
-      <c r="G17" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H17" s="18" t="s">
-        <v>23</v>
+        <v>30</v>
+      </c>
+      <c r="F17" s="18">
+        <v>0</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" s="19" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="16">
+      <c r="B18" s="17">
         <v>46218.5</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F18" s="17">
+        <v>31</v>
+      </c>
+      <c r="F18" s="18">
         <v>4800</v>
       </c>
-      <c r="G18" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H18" s="18" t="s">
-        <v>23</v>
+      <c r="G18" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="19" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="F20" s="14">
+      <c r="A20" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F20" s="15">
         <v>4200</v>
       </c>
-      <c r="H20" s="15">
+      <c r="H20" s="16">
         <v>522.81</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="16">
+      <c r="B21" s="17">
         <v>46205.5</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F21" s="17">
-        <v>0</v>
-      </c>
-      <c r="G21" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H21" s="18" t="s">
-        <v>23</v>
+        <v>33</v>
+      </c>
+      <c r="F21" s="18">
+        <v>0</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="16">
+      <c r="B22" s="17">
         <v>46205.5</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F22" s="17">
+        <v>34</v>
+      </c>
+      <c r="F22" s="18">
         <v>4200</v>
       </c>
-      <c r="G22" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H22" s="18" t="s">
-        <v>23</v>
+      <c r="G22" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="F24" s="14">
+      <c r="A24" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="F24" s="15">
         <v>3000</v>
       </c>
-      <c r="H24" s="15">
+      <c r="H24" s="16">
         <v>355</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="16">
+      <c r="B25" s="17">
         <v>46231.5</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F25" s="17">
+        <v>36</v>
+      </c>
+      <c r="F25" s="18">
         <v>1200</v>
       </c>
-      <c r="G25" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H25" s="18" t="s">
-        <v>23</v>
+      <c r="G25" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H25" s="19" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="16">
+      <c r="B26" s="17">
         <v>46226.5</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F26" s="17">
+        <v>37</v>
+      </c>
+      <c r="F26" s="18">
         <v>1800</v>
       </c>
-      <c r="G26" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H26" s="18" t="s">
-        <v>23</v>
+      <c r="G26" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H26" s="19" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="F28" s="14">
+      <c r="A28" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="F28" s="15">
         <v>1800</v>
       </c>
-      <c r="H28" s="15">
+      <c r="H28" s="16">
         <v>270</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="16">
+      <c r="B29" s="17">
         <v>46224.5</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F29" s="17">
+        <v>39</v>
+      </c>
+      <c r="F29" s="18">
         <v>1800</v>
       </c>
-      <c r="G29" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H29" s="18" t="s">
-        <v>23</v>
+      <c r="G29" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H29" s="19" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="F31" s="14">
+      <c r="A31" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F31" s="15">
         <v>600</v>
       </c>
-      <c r="H31" s="15">
+      <c r="H31" s="16">
         <v>68.33</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="16">
+      <c r="B32" s="17">
         <v>46229.5</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F32" s="17">
-        <v>0</v>
-      </c>
-      <c r="G32" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H32" s="18" t="s">
-        <v>23</v>
+        <v>41</v>
+      </c>
+      <c r="F32" s="18">
+        <v>0</v>
+      </c>
+      <c r="G32" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H32" s="19" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="16">
+      <c r="B33" s="17">
         <v>46225.5</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F33" s="17">
+        <v>42</v>
+      </c>
+      <c r="F33" s="18">
         <v>600</v>
       </c>
-      <c r="G33" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H33" s="18" t="s">
-        <v>23</v>
+      <c r="G33" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H33" s="19" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="F35" s="14">
+      <c r="A35" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F35" s="15">
         <v>600</v>
       </c>
-      <c r="H35" s="15">
+      <c r="H35" s="16">
         <v>72.5</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="16">
+      <c r="B36" s="17">
         <v>46226.5</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F36" s="17">
+        <v>44</v>
+      </c>
+      <c r="F36" s="18">
         <v>600</v>
       </c>
-      <c r="G36" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H36" s="18" t="s">
-        <v>23</v>
+      <c r="G36" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H36" s="19" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="F38" s="14">
-        <v>0</v>
-      </c>
-      <c r="H38" s="15">
+      <c r="A38" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F38" s="15">
+        <v>0</v>
+      </c>
+      <c r="H38" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39" s="16">
+      <c r="B39" s="17">
         <v>46234.5</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F39" s="17">
-        <v>0</v>
-      </c>
-      <c r="G39" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H39" s="18" t="s">
-        <v>23</v>
+        <v>46</v>
+      </c>
+      <c r="F39" s="18">
+        <v>0</v>
+      </c>
+      <c r="G39" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H39" s="19" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="F41" s="14">
-        <v>0</v>
-      </c>
-      <c r="H41" s="15">
+      <c r="A41" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F41" s="15">
+        <v>0</v>
+      </c>
+      <c r="H41" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B42" s="16">
+      <c r="B42" s="17">
         <v>46230.5</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F42" s="17">
-        <v>0</v>
-      </c>
-      <c r="G42" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H42" s="18" t="s">
-        <v>23</v>
+        <v>48</v>
+      </c>
+      <c r="F42" s="18">
+        <v>0</v>
+      </c>
+      <c r="G42" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H42" s="19" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="F44" s="14">
-        <v>0</v>
-      </c>
-      <c r="H44" s="15">
+      <c r="A44" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="F44" s="15">
+        <v>0</v>
+      </c>
+      <c r="H44" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B45" s="16">
+      <c r="B45" s="17">
         <v>46224.5</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F45" s="17">
-        <v>0</v>
-      </c>
-      <c r="G45" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H45" s="18" t="s">
-        <v>23</v>
+        <v>50</v>
+      </c>
+      <c r="F45" s="18">
+        <v>0</v>
+      </c>
+      <c r="G45" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H45" s="19" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="F48" s="20">
+      <c r="A48" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="F48" s="21">
         <v>20400</v>
       </c>
-      <c r="H48" s="21">
+      <c r="H48" s="22">
         <v>1020</v>
       </c>
     </row>

--- a/commission/megan/2026-07.xlsx
+++ b/commission/megan/2026-07.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="46">
   <si>
     <t>Equine Performance Labs, LLC</t>
   </si>
@@ -82,15 +82,15 @@
     <t>The Feiner Equine</t>
   </si>
   <si>
+    <t>—</t>
+  </si>
+  <si>
     <t>Invoice</t>
   </si>
   <si>
     <t>ORD-EPL-1139</t>
   </si>
   <si>
-    <t>—</t>
-  </si>
-  <si>
     <t>ORD-EPL-1138</t>
   </si>
   <si>
@@ -146,24 +146,6 @@
   </si>
   <si>
     <t>ORD-EPL-1153</t>
-  </si>
-  <si>
-    <t>East Fork Equine</t>
-  </si>
-  <si>
-    <t>ORD-EPL-1156</t>
-  </si>
-  <si>
-    <t>Kentucky Equine Medical Associates</t>
-  </si>
-  <si>
-    <t>ORD-EPL-1155</t>
-  </si>
-  <si>
-    <t>Advanced Equine of the Hudson Valley</t>
-  </si>
-  <si>
-    <t>ORD-EPL-1145</t>
   </si>
   <si>
     <t>GRAND TOTAL</t>
@@ -301,7 +283,7 @@
     <xf numFmtId="164" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -657,7 +639,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -768,8 +750,8 @@
       <c r="F10" s="15">
         <v>5400</v>
       </c>
-      <c r="H10" s="16">
-        <v>671.25</v>
+      <c r="H10" s="16" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
@@ -777,19 +759,19 @@
         <v>46217.5</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F11" s="18">
         <v>0</v>
       </c>
       <c r="G11" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H11" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
@@ -797,7 +779,7 @@
         <v>46217.5</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>26</v>
@@ -806,10 +788,10 @@
         <v>4800</v>
       </c>
       <c r="G12" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H12" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
@@ -817,7 +799,7 @@
         <v>46206.5</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>27</v>
@@ -826,10 +808,10 @@
         <v>0</v>
       </c>
       <c r="G13" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H13" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.25">
@@ -837,7 +819,7 @@
         <v>46206.5</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>28</v>
@@ -846,10 +828,10 @@
         <v>600</v>
       </c>
       <c r="G14" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H14" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -859,8 +841,8 @@
       <c r="F16" s="15">
         <v>4800</v>
       </c>
-      <c r="H16" s="16">
-        <v>720</v>
+      <c r="H16" s="16" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
@@ -868,7 +850,7 @@
         <v>46218.5</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>30</v>
@@ -877,10 +859,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H17" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
@@ -888,7 +870,7 @@
         <v>46218.5</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>31</v>
@@ -897,10 +879,10 @@
         <v>4800</v>
       </c>
       <c r="G18" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H18" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -910,8 +892,8 @@
       <c r="F20" s="15">
         <v>4200</v>
       </c>
-      <c r="H20" s="16">
-        <v>522.81</v>
+      <c r="H20" s="16" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
@@ -919,7 +901,7 @@
         <v>46205.5</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>33</v>
@@ -928,10 +910,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H21" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
@@ -939,7 +921,7 @@
         <v>46205.5</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>34</v>
@@ -948,10 +930,10 @@
         <v>4200</v>
       </c>
       <c r="G22" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H22" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -961,8 +943,8 @@
       <c r="F24" s="15">
         <v>3000</v>
       </c>
-      <c r="H24" s="16">
-        <v>355</v>
+      <c r="H24" s="16" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
@@ -970,7 +952,7 @@
         <v>46231.5</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>36</v>
@@ -979,10 +961,10 @@
         <v>1200</v>
       </c>
       <c r="G25" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H25" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
@@ -990,7 +972,7 @@
         <v>46226.5</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>37</v>
@@ -999,10 +981,10 @@
         <v>1800</v>
       </c>
       <c r="G26" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H26" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1012,8 +994,8 @@
       <c r="F28" s="15">
         <v>1800</v>
       </c>
-      <c r="H28" s="16">
-        <v>270</v>
+      <c r="H28" s="16" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.25">
@@ -1021,7 +1003,7 @@
         <v>46224.5</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>39</v>
@@ -1030,10 +1012,10 @@
         <v>1800</v>
       </c>
       <c r="G29" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H29" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1043,8 +1025,8 @@
       <c r="F31" s="15">
         <v>600</v>
       </c>
-      <c r="H31" s="16">
-        <v>68.33</v>
+      <c r="H31" s="16" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.25">
@@ -1052,7 +1034,7 @@
         <v>46229.5</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>41</v>
@@ -1061,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H32" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.25">
@@ -1072,7 +1054,7 @@
         <v>46225.5</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>42</v>
@@ -1081,10 +1063,10 @@
         <v>600</v>
       </c>
       <c r="G33" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H33" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1094,8 +1076,8 @@
       <c r="F35" s="15">
         <v>600</v>
       </c>
-      <c r="H35" s="16">
-        <v>72.5</v>
+      <c r="H35" s="16" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.25">
@@ -1103,7 +1085,7 @@
         <v>46226.5</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>44</v>
@@ -1112,113 +1094,20 @@
         <v>600</v>
       </c>
       <c r="G36" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H36" s="19" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="F38" s="15">
-        <v>0</v>
-      </c>
-      <c r="H38" s="16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39" s="17">
-        <v>46234.5</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F39" s="18">
-        <v>0</v>
-      </c>
-      <c r="G39" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="H39" s="19" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="F41" s="15">
-        <v>0</v>
-      </c>
-      <c r="H41" s="16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B42" s="17">
-        <v>46230.5</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F42" s="18">
-        <v>0</v>
-      </c>
-      <c r="G42" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="H42" s="19" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="F44" s="15">
-        <v>0</v>
-      </c>
-      <c r="H44" s="16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B45" s="17">
-        <v>46224.5</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F45" s="18">
-        <v>0</v>
-      </c>
-      <c r="G45" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="H45" s="19" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="F48" s="21">
+      <c r="F39" s="21">
         <v>20400</v>
       </c>
-      <c r="H48" s="22">
+      <c r="H39" s="22">
         <v>1020</v>
       </c>
     </row>

--- a/commission/megan/2026-07.xlsx
+++ b/commission/megan/2026-07.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
   <si>
     <t>Equine Performance Labs, LLC</t>
   </si>
@@ -52,7 +52,7 @@
     <t>✗ MISSED — Standard waterfall</t>
   </si>
   <si>
-    <t>Fallback: standard 5% / 6% / 7.5% / 10% waterfall on $20,400</t>
+    <t>Fallback: standard 5% / 6% / 7.5% / 10% waterfall on $18,600 collected</t>
   </si>
   <si>
     <t>Account / Date</t>
@@ -82,64 +82,46 @@
     <t>The Feiner Equine</t>
   </si>
   <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>Invoice</t>
-  </si>
-  <si>
-    <t>ORD-EPL-1139</t>
+    <t>Payment</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1132</t>
   </si>
   <si>
     <t>ORD-EPL-1138</t>
   </si>
   <si>
-    <t>ORD-EPL-1133</t>
-  </si>
-  <si>
-    <t>ORD-EPL-1132</t>
-  </si>
-  <si>
-    <t>Equine Sports Medicine</t>
-  </si>
-  <si>
-    <t>ORD-EPL-1142</t>
-  </si>
-  <si>
-    <t>ORD-EPL-1141</t>
+    <t>KBS Performance Horse Services</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1123</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1149</t>
+  </si>
+  <si>
+    <t>WinStar Farm LLC</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1098</t>
+  </si>
+  <si>
+    <t>Spruce Lane Farm</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1099</t>
   </si>
   <si>
     <t>Running S Equine</t>
   </si>
   <si>
-    <t>ORD-EPL-1131</t>
-  </si>
-  <si>
-    <t>ORD-EPL-1130</t>
-  </si>
-  <si>
-    <t>Ocala Equine Hospital</t>
-  </si>
-  <si>
-    <t>CINV-EPL-1020</t>
-  </si>
-  <si>
-    <t>ORD-EPL-1152</t>
-  </si>
-  <si>
-    <t>Springhill Equine Veterinary Clinic</t>
-  </si>
-  <si>
-    <t>ORD-EPL-1146</t>
-  </si>
-  <si>
-    <t>KBS Performance Horse Services</t>
-  </si>
-  <si>
-    <t>ORD-EPL-1154</t>
-  </si>
-  <si>
-    <t>ORD-EPL-1149</t>
+    <t>ORD-EPL-1126</t>
+  </si>
+  <si>
+    <t>Kennedy Equine</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1090</t>
   </si>
   <si>
     <t>East Coast Equine Veterinary</t>
@@ -155,12 +137,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -223,7 +206,11 @@
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="7A7974"/>
+      <color rgb="0F5E4F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="0F5E4F"/>
     </font>
     <font>
       <b/>
@@ -260,7 +247,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -283,18 +270,22 @@
     <xf numFmtId="164" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -639,7 +630,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -660,7 +651,7 @@
         <v>1</v>
       </c>
       <c r="H1" s="3">
-        <v>1020</v>
+        <v>930</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -714,7 +705,7 @@
         <v>13</v>
       </c>
       <c r="B7" s="11">
-        <v>1020</v>
+        <v>930</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -750,365 +741,265 @@
       <c r="F10" s="15">
         <v>5400</v>
       </c>
-      <c r="H10" s="16" t="s">
-        <v>23</v>
+      <c r="H10" s="16">
+        <v>270</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="17">
-        <v>46217.5</v>
-      </c>
-      <c r="C11" s="2" t="s">
+        <v>46209.5</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="18">
-        <v>0</v>
-      </c>
-      <c r="G11" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11" s="19" t="s">
-        <v>23</v>
+      <c r="F11" s="19">
+        <v>600</v>
+      </c>
+      <c r="G11" s="20">
+        <v>0.05</v>
+      </c>
+      <c r="H11" s="21">
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" s="17">
         <v>46217.5</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>24</v>
+      <c r="C12" s="18" t="s">
+        <v>23</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="19">
+        <v>4800</v>
+      </c>
+      <c r="G12" s="20">
+        <v>0.05</v>
+      </c>
+      <c r="H12" s="21">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="F12" s="18">
+      <c r="F14" s="15">
+        <v>5400</v>
+      </c>
+      <c r="H14" s="16">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="17">
+        <v>46213.5</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="19">
         <v>4800</v>
       </c>
-      <c r="G12" s="19" t="s">
+      <c r="G15" s="20">
+        <v>0.05</v>
+      </c>
+      <c r="H15" s="21">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="17">
+        <v>46226.5</v>
+      </c>
+      <c r="C16" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="H12" s="19" t="s">
+      <c r="E16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="19">
+        <v>600</v>
+      </c>
+      <c r="G16" s="20">
+        <v>0.05</v>
+      </c>
+      <c r="H16" s="21">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" s="15">
+        <v>5400</v>
+      </c>
+      <c r="H18" s="16">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="17">
+        <v>46226.5</v>
+      </c>
+      <c r="C19" s="18" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="17">
-        <v>46206.5</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F13" s="18">
-        <v>0</v>
-      </c>
-      <c r="G13" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="H13" s="19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B14" s="17">
-        <v>46206.5</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F14" s="18">
+      <c r="E19" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19" s="19">
+        <v>5400</v>
+      </c>
+      <c r="G19" s="20">
+        <v>0.05</v>
+      </c>
+      <c r="H19" s="21">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" s="15">
         <v>600</v>
       </c>
-      <c r="G14" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="H14" s="19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="15">
-        <v>4800</v>
-      </c>
-      <c r="H16" s="16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="17">
-        <v>46218.5</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="H21" s="16">
         <v>30</v>
-      </c>
-      <c r="F17" s="18">
-        <v>0</v>
-      </c>
-      <c r="G17" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="H17" s="19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="17">
-        <v>46218.5</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F18" s="18">
-        <v>4800</v>
-      </c>
-      <c r="G18" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="H18" s="19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="F20" s="15">
-        <v>4200</v>
-      </c>
-      <c r="H20" s="16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="17">
-        <v>46205.5</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F21" s="18">
-        <v>0</v>
-      </c>
-      <c r="G21" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="H21" s="19" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="17">
-        <v>46205.5</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>24</v>
+        <v>46209.5</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>23</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F22" s="18">
-        <v>4200</v>
-      </c>
-      <c r="G22" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="H22" s="19" t="s">
-        <v>23</v>
+        <v>32</v>
+      </c>
+      <c r="F22" s="19">
+        <v>600</v>
+      </c>
+      <c r="G22" s="20">
+        <v>0.05</v>
+      </c>
+      <c r="H22" s="21">
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F24" s="15">
-        <v>3000</v>
-      </c>
-      <c r="H24" s="16" t="s">
-        <v>23</v>
+        <v>600</v>
+      </c>
+      <c r="H24" s="16">
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="17">
-        <v>46231.5</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>24</v>
+        <v>46218.5</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>23</v>
       </c>
       <c r="E25" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F25" s="19">
+        <v>600</v>
+      </c>
+      <c r="G25" s="20">
+        <v>0.05</v>
+      </c>
+      <c r="H25" s="21">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="F27" s="15">
+        <v>600</v>
+      </c>
+      <c r="H27" s="16">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="17">
+        <v>46219.5</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F25" s="18">
-        <v>1200</v>
-      </c>
-      <c r="G25" s="19" t="s">
+      <c r="F28" s="19">
+        <v>600</v>
+      </c>
+      <c r="G28" s="20">
+        <v>0.05</v>
+      </c>
+      <c r="H28" s="21">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F30" s="15">
+        <v>600</v>
+      </c>
+      <c r="H30" s="16">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="17">
+        <v>46227.5</v>
+      </c>
+      <c r="C31" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="H25" s="19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="17">
-        <v>46226.5</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F26" s="18">
-        <v>1800</v>
-      </c>
-      <c r="G26" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="H26" s="19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="s">
+      <c r="E31" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F28" s="15">
-        <v>1800</v>
-      </c>
-      <c r="H28" s="16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="17">
-        <v>46224.5</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F31" s="19">
+        <v>600</v>
+      </c>
+      <c r="G31" s="20">
+        <v>0.05</v>
+      </c>
+      <c r="H31" s="21">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="F29" s="18">
-        <v>1800</v>
-      </c>
-      <c r="G29" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="H29" s="19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="F31" s="15">
-        <v>600</v>
-      </c>
-      <c r="H31" s="16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="17">
-        <v>46229.5</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F32" s="18">
-        <v>0</v>
-      </c>
-      <c r="G32" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="H32" s="19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="17">
-        <v>46225.5</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F33" s="18">
-        <v>600</v>
-      </c>
-      <c r="G33" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="H33" s="19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="F35" s="15">
-        <v>600</v>
-      </c>
-      <c r="H35" s="16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="17">
-        <v>46226.5</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F36" s="18">
-        <v>600</v>
-      </c>
-      <c r="G36" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="H36" s="19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="F39" s="21">
-        <v>20400</v>
-      </c>
-      <c r="H39" s="22">
-        <v>1020</v>
+      <c r="F34" s="23">
+        <v>18600</v>
+      </c>
+      <c r="H34" s="24">
+        <v>930</v>
       </c>
     </row>
   </sheetData>
